--- a/documents/cuarto/segundo_cuatrimestre/metaheuristicas/trabajo_final/software/cec2017real/code/results_sca/results_cec2017_10.xlsx
+++ b/documents/cuarto/segundo_cuatrimestre/metaheuristicas/trabajo_final/software/cec2017real/code/results_sca/results_cec2017_10.xlsx
@@ -598,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6860229250</v>
+        <v>6894966000</v>
       </c>
       <c r="D2" t="n">
         <v>109501179790</v>
@@ -625,7 +625,7 @@
         <v>3036.3088</v>
       </c>
       <c r="L2" t="n">
-        <v>1908.6809375</v>
+        <v>1918.072972222222</v>
       </c>
       <c r="M2" t="n">
         <v>2497.81383</v>
@@ -640,10 +640,10 @@
         <v>24088.197</v>
       </c>
       <c r="Q2" t="n">
-        <v>85730.27489999999</v>
+        <v>85730.2749</v>
       </c>
       <c r="R2" t="n">
-        <v>635.45814</v>
+        <v>635.4581400000001</v>
       </c>
       <c r="S2" t="n">
         <v>253.54925</v>
@@ -670,7 +670,7 @@
         <v>421.51517</v>
       </c>
       <c r="AA2" t="n">
-        <v>857.4111300000001</v>
+        <v>857.41113</v>
       </c>
       <c r="AB2" t="n">
         <v>1494.34038</v>
@@ -699,7 +699,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6304875000</v>
+        <v>6389201272.727273</v>
       </c>
       <c r="D3" t="n">
         <v>55423403390</v>
@@ -726,7 +726,7 @@
         <v>2356.1004</v>
       </c>
       <c r="L3" t="n">
-        <v>1853.5586875</v>
+        <v>1865.730638888889</v>
       </c>
       <c r="M3" t="n">
         <v>1207.37122</v>
@@ -744,7 +744,7 @@
         <v>61233.1404</v>
       </c>
       <c r="R3" t="n">
-        <v>492.9833399999999</v>
+        <v>492.98334</v>
       </c>
       <c r="S3" t="n">
         <v>249.96783</v>
@@ -762,19 +762,19 @@
         <v>260.85254</v>
       </c>
       <c r="X3" t="n">
-        <v>880.3481600000001</v>
+        <v>880.34816</v>
       </c>
       <c r="Y3" t="n">
         <v>388.44554</v>
       </c>
       <c r="Z3" t="n">
-        <v>417.3077499999999</v>
+        <v>417.30775</v>
       </c>
       <c r="AA3" t="n">
         <v>751.77139</v>
       </c>
       <c r="AB3" t="n">
-        <v>977.94813</v>
+        <v>977.9481300000001</v>
       </c>
       <c r="AC3" t="n">
         <v>415.52576</v>
@@ -800,7 +800,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5098092250</v>
+        <v>5125704090.909091</v>
       </c>
       <c r="D4" t="n">
         <v>30699635390</v>
@@ -827,7 +827,7 @@
         <v>2290.389</v>
       </c>
       <c r="L4" t="n">
-        <v>1704.2245</v>
+        <v>1725.828166666667</v>
       </c>
       <c r="M4" t="n">
         <v>971.8404699999999</v>
@@ -839,7 +839,7 @@
         <v>2219312.112</v>
       </c>
       <c r="P4" t="n">
-        <v>4717.589099999999</v>
+        <v>4717.5891</v>
       </c>
       <c r="Q4" t="n">
         <v>51538.4454</v>
@@ -872,7 +872,7 @@
         <v>407.32726</v>
       </c>
       <c r="AA4" t="n">
-        <v>697.5596800000001</v>
+        <v>697.55968</v>
       </c>
       <c r="AB4" t="n">
         <v>798.9523</v>
@@ -881,7 +881,7 @@
         <v>413.38552</v>
       </c>
       <c r="AD4" t="n">
-        <v>628.74019</v>
+        <v>628.7401900000001</v>
       </c>
       <c r="AE4" t="n">
         <v>473.81634</v>
@@ -901,7 +901,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>4465395416.666667</v>
+        <v>4435489363.636364</v>
       </c>
       <c r="D5" t="n">
         <v>17413190590</v>
@@ -928,7 +928,7 @@
         <v>1774.44431</v>
       </c>
       <c r="L5" t="n">
-        <v>1600.14525</v>
+        <v>1608.571388888889</v>
       </c>
       <c r="M5" t="n">
         <v>823.76882</v>
@@ -973,16 +973,16 @@
         <v>403.63988</v>
       </c>
       <c r="AA5" t="n">
-        <v>668.5752199999999</v>
+        <v>668.5752200000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>735.0074099999999</v>
+        <v>735.00741</v>
       </c>
       <c r="AC5" t="n">
         <v>409.39408</v>
       </c>
       <c r="AD5" t="n">
-        <v>593.77757</v>
+        <v>593.7775700000001</v>
       </c>
       <c r="AE5" t="n">
         <v>445.91297</v>
@@ -1002,7 +1002,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>3385067250</v>
+        <v>3279687818.181818</v>
       </c>
       <c r="D6" t="n">
         <v>7084954740</v>
@@ -1029,7 +1029,7 @@
         <v>852.58987</v>
       </c>
       <c r="L6" t="n">
-        <v>1547.9235</v>
+        <v>1559.130444444444</v>
       </c>
       <c r="M6" t="n">
         <v>710.70439</v>
@@ -1065,7 +1065,7 @@
         <v>220.95203</v>
       </c>
       <c r="X6" t="n">
-        <v>412.59384</v>
+        <v>412.5938399999999</v>
       </c>
       <c r="Y6" t="n">
         <v>370.34952</v>
@@ -1103,7 +1103,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>2463951000</v>
+        <v>2459176181.818182</v>
       </c>
       <c r="D7" t="n">
         <v>1675644700</v>
@@ -1130,7 +1130,7 @@
         <v>506.11914</v>
       </c>
       <c r="L7" t="n">
-        <v>1374.712275</v>
+        <v>1405.164911111111</v>
       </c>
       <c r="M7" t="n">
         <v>402.11235</v>
@@ -1175,7 +1175,7 @@
         <v>396.04547</v>
       </c>
       <c r="AA7" t="n">
-        <v>556.4640499999999</v>
+        <v>556.46405</v>
       </c>
       <c r="AB7" t="n">
         <v>579.31065</v>
@@ -1204,7 +1204,7 @@
         <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>1628104583.333333</v>
+        <v>1673109636.363636</v>
       </c>
       <c r="D8" t="n">
         <v>46802639.3</v>
@@ -1231,7 +1231,7 @@
         <v>367.47574</v>
       </c>
       <c r="L8" t="n">
-        <v>1349.56765</v>
+        <v>1372.423411111111</v>
       </c>
       <c r="M8" t="n">
         <v>272.30312</v>
@@ -1276,10 +1276,10 @@
         <v>391.51387</v>
       </c>
       <c r="AA8" t="n">
-        <v>532.7394400000001</v>
+        <v>532.7394399999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>531.6558699999999</v>
+        <v>531.65587</v>
       </c>
       <c r="AC8" t="n">
         <v>402.52016</v>
@@ -1291,7 +1291,7 @@
         <v>386.54404</v>
       </c>
       <c r="AF8" t="n">
-        <v>840171.0900000001</v>
+        <v>840171.09</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>1518143500</v>
+        <v>1553152090.909091</v>
       </c>
       <c r="D9" t="n">
         <v>15879312.7</v>
@@ -1332,7 +1332,7 @@
         <v>231.68251</v>
       </c>
       <c r="L9" t="n">
-        <v>1273.6954</v>
+        <v>1304.981411111111</v>
       </c>
       <c r="M9" t="n">
         <v>179.258804</v>
@@ -1341,7 +1341,7 @@
         <v>27658570.7</v>
       </c>
       <c r="O9" t="n">
-        <v>80842.91</v>
+        <v>80842.90999999999</v>
       </c>
       <c r="P9" t="n">
         <v>924.32642</v>
@@ -1406,7 +1406,7 @@
         <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>1196109500</v>
+        <v>1201842272.727273</v>
       </c>
       <c r="D10" t="n">
         <v>7819976.3</v>
@@ -1433,7 +1433,7 @@
         <v>180.05111</v>
       </c>
       <c r="L10" t="n">
-        <v>1258.516525</v>
+        <v>1286.724633333333</v>
       </c>
       <c r="M10" t="n">
         <v>137.176844</v>
@@ -1493,7 +1493,7 @@
         <v>352.44991</v>
       </c>
       <c r="AF10" t="n">
-        <v>673462.9400000001</v>
+        <v>673462.9399999999</v>
       </c>
       <c r="AG10" t="n">
         <v>10</v>
@@ -1507,7 +1507,7 @@
         <v>60</v>
       </c>
       <c r="C11" t="n">
-        <v>904889066.6666666</v>
+        <v>909453954.5454545</v>
       </c>
       <c r="D11" t="n">
         <v>4172891.8</v>
@@ -1534,7 +1534,7 @@
         <v>144.65579</v>
       </c>
       <c r="L11" t="n">
-        <v>1233.737466666667</v>
+        <v>1258.114548571428</v>
       </c>
       <c r="M11" t="n">
         <v>122.066778</v>
@@ -1608,7 +1608,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>747223650</v>
+        <v>774547454.5454545</v>
       </c>
       <c r="D12" t="n">
         <v>1853728.6</v>
@@ -1635,7 +1635,7 @@
         <v>115.159363</v>
       </c>
       <c r="L12" t="n">
-        <v>1233.737466666667</v>
+        <v>1258.114548571428</v>
       </c>
       <c r="M12" t="n">
         <v>100.937187</v>
@@ -1656,7 +1656,7 @@
         <v>185.024795</v>
       </c>
       <c r="S12" t="n">
-        <v>73.26106100000001</v>
+        <v>73.261061</v>
       </c>
       <c r="T12" t="n">
         <v>107925.81</v>
@@ -1709,7 +1709,7 @@
         <v>80</v>
       </c>
       <c r="C13" t="n">
-        <v>650240375</v>
+        <v>668747518.1818181</v>
       </c>
       <c r="D13" t="n">
         <v>1462220.7</v>
@@ -1736,7 +1736,7 @@
         <v>107.218056</v>
       </c>
       <c r="L13" t="n">
-        <v>1192.6896</v>
+        <v>1208.530148571429</v>
       </c>
       <c r="M13" t="n">
         <v>87.75618299999999</v>
@@ -1751,7 +1751,7 @@
         <v>181.760764</v>
       </c>
       <c r="Q13" t="n">
-        <v>563.1560400000001</v>
+        <v>563.15604</v>
       </c>
       <c r="R13" t="n">
         <v>166.764265</v>
@@ -1760,7 +1760,7 @@
         <v>69.98058599999999</v>
       </c>
       <c r="T13" t="n">
-        <v>77881.76800000001</v>
+        <v>77881.768</v>
       </c>
       <c r="U13" t="n">
         <v>1532.30139</v>
@@ -1810,7 +1810,7 @@
         <v>90</v>
       </c>
       <c r="C14" t="n">
-        <v>593499483.3333334</v>
+        <v>606848363.6363636</v>
       </c>
       <c r="D14" t="n">
         <v>1011496.2</v>
@@ -1837,10 +1837,10 @@
         <v>94.600341</v>
       </c>
       <c r="L14" t="n">
-        <v>1192.6896</v>
+        <v>1208.530148571429</v>
       </c>
       <c r="M14" t="n">
-        <v>76.73589200000001</v>
+        <v>76.73589199999999</v>
       </c>
       <c r="N14" t="n">
         <v>8916911</v>
@@ -1867,7 +1867,7 @@
         <v>569.23062</v>
       </c>
       <c r="V14" t="n">
-        <v>99.89069600000001</v>
+        <v>99.89069599999999</v>
       </c>
       <c r="W14" t="n">
         <v>151.52715</v>
@@ -1885,7 +1885,7 @@
         <v>455.17618</v>
       </c>
       <c r="AB14" t="n">
-        <v>451.8834699999999</v>
+        <v>451.88347</v>
       </c>
       <c r="AC14" t="n">
         <v>401.03746</v>
@@ -1911,7 +1911,7 @@
         <v>100</v>
       </c>
       <c r="C15" t="n">
-        <v>535089316.6666667</v>
+        <v>543128181.8181819</v>
       </c>
       <c r="D15" t="n">
         <v>975369.3</v>
@@ -1938,7 +1938,7 @@
         <v>86.510178</v>
       </c>
       <c r="L15" t="n">
-        <v>1183.403466666667</v>
+        <v>1196.590834285714</v>
       </c>
       <c r="M15" t="n">
         <v>74.863823</v>
@@ -1959,13 +1959,13 @@
         <v>144.781354</v>
       </c>
       <c r="S15" t="n">
-        <v>66.09229400000001</v>
+        <v>66.092294</v>
       </c>
       <c r="T15" t="n">
-        <v>72266.20300000001</v>
+        <v>72266.20299999999</v>
       </c>
       <c r="U15" t="n">
-        <v>546.1316399999999</v>
+        <v>546.1316400000001</v>
       </c>
       <c r="V15" t="n">
         <v>90.14100499999999</v>
@@ -1986,7 +1986,7 @@
         <v>453.71321</v>
       </c>
       <c r="AB15" t="n">
-        <v>451.8834699999999</v>
+        <v>451.88347</v>
       </c>
       <c r="AC15" t="n">
         <v>401.03746</v>
@@ -1995,7 +1995,7 @@
         <v>473.4207</v>
       </c>
       <c r="AE15" t="n">
-        <v>336.27479</v>
+        <v>336.2747900000001</v>
       </c>
       <c r="AF15" t="n">
         <v>486408.58</v>
